--- a/artfynd/A 22966-2020 artfynd.xlsx
+++ b/artfynd/A 22966-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22966-2020 artfynd.xlsx
+++ b/artfynd/A 22966-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105373759</v>
+        <v>115287785</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
+        <v>57414</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mattjärnen, Hl</t>
+          <t>Grästärnen öster, Grästjärn, Lindome, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335545.4058457818</v>
+        <v>335547</v>
       </c>
       <c r="R2" t="n">
-        <v>6387030.534947467</v>
+        <v>6387044</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +761,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sjungande Talltita, validerad genom Merlin fågerapp. Flera mesar i områet vid samma tillfälle, framförallt Svartmes, Talgoxe och Kungsfågel</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +786,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115287785</v>
+        <v>115287920</v>
       </c>
       <c r="B3" t="n">
-        <v>57414</v>
+        <v>56478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,44 +810,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grästärnen öster, Grästjärn, Lindome, Hl</t>
@@ -883,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sjungande Talltita, validerad genom Merlin fågerapp. Flera mesar i områet vid samma tillfälle, framförallt Svartmes, Talgoxe och Kungsfågel</t>
+          <t>Rikligt tjäderspillning vid spelplats aktiv 2023</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115287920</v>
+        <v>115783924</v>
       </c>
       <c r="B4" t="n">
         <v>56478</v>
@@ -944,20 +943,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grästärnen öster, Grästjärn, Lindome, Hl</t>
+          <t>Höjd Lindome 3:2 N, Grästjärn, Lindome, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335547</v>
+        <v>335627</v>
       </c>
       <c r="R4" t="n">
-        <v>6387044</v>
+        <v>6386883</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,17 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt tjäderspillning vid spelplats aktiv 2023</t>
+          <t>Tjäderspillning i närheten där tjädertupp befann sig 2023</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,123 +1023,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>115783924</v>
-      </c>
-      <c r="B5" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Höjd Lindome 3:2 N, Grästjärn, Lindome, Hl</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>335627</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6386883</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Mölndal</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Lindome</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-04-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-04-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tjäderspillning i närheten där tjädertupp befann sig 2023</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mats Foss</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mats Foss</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22966-2020 artfynd.xlsx
+++ b/artfynd/A 22966-2020 artfynd.xlsx
@@ -801,12 +801,7 @@
         <v>115287920</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,12 +907,7 @@
         <v>115783924</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22966-2020 artfynd.xlsx
+++ b/artfynd/A 22966-2020 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>115287920</v>
       </c>
       <c r="B3" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>115783924</v>
       </c>
       <c r="B4" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22966-2020 artfynd.xlsx
+++ b/artfynd/A 22966-2020 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>115287920</v>
       </c>
       <c r="B3" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>115783924</v>
       </c>
       <c r="B4" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22966-2020 artfynd.xlsx
+++ b/artfynd/A 22966-2020 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>115287920</v>
       </c>
       <c r="B3" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>115783924</v>
       </c>
       <c r="B4" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
